--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="112">
   <si>
     <t>_reportFile</t>
   </si>
@@ -70,6 +70,21 @@
     <t>http://localhost:8888/automation.html</t>
   </si>
   <si>
+    <t>carbon-capture.report.json</t>
+  </si>
+  <si>
+    <t>carbon-capture</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:14:10.604Z</t>
+  </si>
+  <si>
+    <t>Honeywell Carbon Capture Technology to Help Transform Shuttered Power Plant Into Fertilizer Facility Supporting U.S. Farmers</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/carbon-capture.html</t>
+  </si>
+  <si>
     <t>customer-stories.report.json</t>
   </si>
   <si>
@@ -85,6 +100,36 @@
     <t>http://localhost:8888/customer-stories.html</t>
   </si>
   <si>
+    <t>dangote.report.json</t>
+  </si>
+  <si>
+    <t>dangote</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:14:17.645Z</t>
+  </si>
+  <si>
+    <t>Honeywell to Help Dangote Double Production Capabilities at Africa’s Largest Refinery</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/dangote.html</t>
+  </si>
+  <si>
+    <t>energy-storage.report.json</t>
+  </si>
+  <si>
+    <t>energy-storage</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:13:42.056Z</t>
+  </si>
+  <si>
+    <t>Get Ahead with Energy Storage or Risk Getting Left Behind | Honeywell</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/energy-storage.html</t>
+  </si>
+  <si>
     <t>energy-transition.report.json</t>
   </si>
   <si>
@@ -118,6 +163,21 @@
     <t>http://localhost:8888/future-of-aviation.html</t>
   </si>
   <si>
+    <t>gas-detection.report.json</t>
+  </si>
+  <si>
+    <t>gas-detection</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:13:48.702Z</t>
+  </si>
+  <si>
+    <t>Gas Detection for Semiconductor Manufacturing Plants</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/gas-detection.html</t>
+  </si>
+  <si>
     <t>honeywell-full.report.json</t>
   </si>
   <si>
@@ -133,6 +193,21 @@
     <t>http://localhost:8888/honeywell-full.html</t>
   </si>
   <si>
+    <t>hotel-future.report.json</t>
+  </si>
+  <si>
+    <t>hotel-future</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:14:03.442Z</t>
+  </si>
+  <si>
+    <t>Is Your Hotel Ready for the Future? 4 Areas to Assess Today</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/hotel-future.html</t>
+  </si>
+  <si>
     <t>industries.report.json</t>
   </si>
   <si>
@@ -146,6 +221,21 @@
   </si>
   <si>
     <t>http://localhost:8888/industries.html</t>
+  </si>
+  <si>
+    <t>ot-cybersecurity.report.json</t>
+  </si>
+  <si>
+    <t>ot-cybersecurity</t>
+  </si>
+  <si>
+    <t>2026-04-30T19:13:56.507Z</t>
+  </si>
+  <si>
+    <t>Omdia Names Honeywell A Market Leader in OT Cybersecurity Services</t>
+  </si>
+  <si>
+    <t>http://localhost:8888/ot-cybersecurity.html</t>
   </si>
   <si>
     <t>us/en.report.json</t>
@@ -687,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -832,16 +922,16 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -850,30 +940,30 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>33</v>
-      </c>
-      <c r="J5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -882,18 +972,18 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -905,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
@@ -914,205 +1004,397 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
         <v>42</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
       <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>48</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="I9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
+      <c r="J9" t="s">
         <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="J10" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" t="s">
         <v>64</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D14" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E14" t="s">
         <v>78</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F14" t="s">
         <v>79</v>
       </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
         <v>80</v>
       </c>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="I14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
